--- a/최종본/01_구매목록/구입항목_정리표.xlsx
+++ b/최종본/01_구매목록/구입항목_정리표.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11020"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kwg/Desktop/mydrive/project/Toccata/최종본/01_구매목록/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12A35E82-1A70-7449-9613-29F68D3058D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7457EB36-89FB-C749-8115-1D357A705452}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="17300" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="21800" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="구입항목" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="67">
   <si>
     <t>품목</t>
   </si>
@@ -216,6 +216,24 @@
   </si>
   <si>
     <t>M3 방진 댐퍼(그로밋) 20개</t>
+  </si>
+  <si>
+    <t>o</t>
+  </si>
+  <si>
+    <t>O</t>
+  </si>
+  <si>
+    <t>딴걸로 해보기</t>
+  </si>
+  <si>
+    <t>https://www.eleparts.co.kr/goods/view?no=19324904</t>
+  </si>
+  <si>
+    <t>https://www.devicemart.co.kr/goods/view?no=14991278</t>
+  </si>
+  <si>
+    <t>링크 변경</t>
   </si>
 </sst>
 </file>
@@ -225,7 +243,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0&quot;원&quot;"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -239,6 +257,12 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Carlito"/>
     </font>
   </fonts>
@@ -293,10 +317,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -313,15 +338,17 @@
     <xf numFmtId="164" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -338,13 +365,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="PurchaseItemsTable" displayName="PurchaseItemsTable" ref="A1:E30" totalsRowShown="0">
-  <tableColumns count="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="PurchaseItemsTable" displayName="PurchaseItemsTable" ref="A1:F30" totalsRowShown="0">
+  <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="품목"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="단가"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="갯수"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="금액"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="사이트 링크"/>
+    <tableColumn id="6" xr3:uid="{625DFF2C-CD22-DE47-AE83-F0A9D948BB1A}" name="링크 변경"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -545,17 +573,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E31"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <dimension ref="A1:I31"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="1" max="1" width="35.1640625" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="10" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="33.25" customHeight="1">
+    <row r="1" spans="1:9" ht="33.25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -571,8 +599,11 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="F1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="7" t="s">
         <v>32</v>
       </c>
@@ -590,7 +621,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:9">
       <c r="A3" s="7" t="s">
         <v>33</v>
       </c>
@@ -607,8 +638,11 @@
       <c r="E3" s="7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="1:5">
+      <c r="F3" s="11" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="7" t="s">
         <v>34</v>
       </c>
@@ -625,8 +659,11 @@
       <c r="E4" s="7" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" spans="1:5">
+      <c r="F4" s="11" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="7" t="s">
         <v>35</v>
       </c>
@@ -644,7 +681,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:9">
       <c r="A6" s="7" t="s">
         <v>36</v>
       </c>
@@ -662,7 +699,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:9">
       <c r="A7" s="7" t="s">
         <v>37</v>
       </c>
@@ -680,7 +717,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:9">
       <c r="A8" s="7" t="s">
         <v>38</v>
       </c>
@@ -698,7 +735,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:9">
       <c r="A9" s="8" t="s">
         <v>39</v>
       </c>
@@ -715,8 +752,11 @@
       <c r="E9" s="8" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="10" spans="1:5">
+      <c r="I9" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="8" t="s">
         <v>40</v>
       </c>
@@ -733,8 +773,11 @@
       <c r="E10" s="8" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="11" spans="1:5">
+      <c r="I10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="8" t="s">
         <v>41</v>
       </c>
@@ -751,8 +794,11 @@
       <c r="E11" s="8" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="12" spans="1:5">
+      <c r="I11" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="8" t="s">
         <v>42</v>
       </c>
@@ -769,8 +815,11 @@
       <c r="E12" s="8" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="13" spans="1:5">
+      <c r="I12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="8" t="s">
         <v>43</v>
       </c>
@@ -787,8 +836,11 @@
       <c r="E13" s="8" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="14" spans="1:5">
+      <c r="I13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" s="8" t="s">
         <v>44</v>
       </c>
@@ -805,8 +857,11 @@
       <c r="E14" s="8" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="15" spans="1:5">
+      <c r="I14" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15" s="8" t="s">
         <v>45</v>
       </c>
@@ -823,8 +878,11 @@
       <c r="E15" s="8" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="16" spans="1:5">
+      <c r="I15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
       <c r="A16" s="8" t="s">
         <v>46</v>
       </c>
@@ -841,8 +899,11 @@
       <c r="E16" s="8" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="17" spans="1:5">
+      <c r="I16" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
       <c r="A17" s="8" t="s">
         <v>47</v>
       </c>
@@ -859,8 +920,11 @@
       <c r="E17" s="8" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="18" spans="1:5">
+      <c r="I17" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
       <c r="A18" s="9" t="s">
         <v>48</v>
       </c>
@@ -877,8 +941,11 @@
       <c r="E18" s="9" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="19" spans="1:5">
+      <c r="I18" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
       <c r="A19" s="9" t="s">
         <v>49</v>
       </c>
@@ -895,8 +962,11 @@
       <c r="E19" s="9" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="20" spans="1:5">
+      <c r="I19" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
       <c r="A20" s="9" t="s">
         <v>50</v>
       </c>
@@ -913,8 +983,11 @@
       <c r="E20" s="9" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="21" spans="1:5">
+      <c r="I20" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
       <c r="A21" s="9" t="s">
         <v>51</v>
       </c>
@@ -931,8 +1004,11 @@
       <c r="E21" s="9" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="22" spans="1:5">
+      <c r="I21" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
       <c r="A22" s="9" t="s">
         <v>52</v>
       </c>
@@ -949,8 +1025,11 @@
       <c r="E22" s="9" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="23" spans="1:5">
+      <c r="I22" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
       <c r="A23" s="9" t="s">
         <v>53</v>
       </c>
@@ -967,8 +1046,11 @@
       <c r="E23" s="9" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="24" spans="1:5">
+      <c r="I23" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
       <c r="A24" s="10" t="s">
         <v>54</v>
       </c>
@@ -985,8 +1067,11 @@
       <c r="E24" s="10" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="25" spans="1:5">
+      <c r="I24" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
       <c r="A25" s="10" t="s">
         <v>55</v>
       </c>
@@ -1003,8 +1088,11 @@
       <c r="E25" s="10" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="26" spans="1:5">
+      <c r="I25" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
       <c r="A26" s="10" t="s">
         <v>56</v>
       </c>
@@ -1021,8 +1109,11 @@
       <c r="E26" s="10" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="27" spans="1:5">
+      <c r="I26" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
       <c r="A27" s="10" t="s">
         <v>57</v>
       </c>
@@ -1039,8 +1130,11 @@
       <c r="E27" s="10" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="28" spans="1:5">
+      <c r="I27" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
       <c r="A28" s="10" t="s">
         <v>58</v>
       </c>
@@ -1057,8 +1151,11 @@
       <c r="E28" s="10" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="29" spans="1:5">
+      <c r="I28" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
       <c r="A29" s="10" t="s">
         <v>59</v>
       </c>
@@ -1075,8 +1172,11 @@
       <c r="E29" s="10" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="30" spans="1:5">
+      <c r="I29" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
       <c r="A30" s="10" t="s">
         <v>60</v>
       </c>
@@ -1093,8 +1193,11 @@
       <c r="E30" s="10" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" ht="16">
+      <c r="I30" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="16">
       <c r="A31" s="4" t="s">
         <v>5</v>
       </c>
@@ -1137,11 +1240,13 @@
     <hyperlink ref="E21" r:id="rId27" tooltip="판매 페이지 열기" xr:uid="{2B2957E7-5532-8048-8EAC-1936CC63A680}"/>
     <hyperlink ref="E22" r:id="rId28" tooltip="판매 페이지 열기" xr:uid="{35704C0D-D3ED-D440-92BF-DC0E70F09608}"/>
     <hyperlink ref="E23" r:id="rId29" tooltip="판매 페이지 열기" xr:uid="{1B78E040-A00C-5E47-9274-0CD760A3C12C}"/>
+    <hyperlink ref="F3" r:id="rId30" xr:uid="{D13EF5AB-23FA-2C4E-9EBD-835CB92CD1F7}"/>
+    <hyperlink ref="F4" r:id="rId31" tooltip="https://www.devicemart.co.kr/goods/view?no=14991278" xr:uid="{148897CE-C680-484C-90E2-57DC175647A4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <tableParts count="1">
-    <tablePart r:id="rId30"/>
+    <tablePart r:id="rId32"/>
   </tableParts>
 </worksheet>
 </file>